--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3935,6 +3935,125 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125843309</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58325</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sumpskogen vid E12, Umeälvens delta och slätter, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>761593</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7076869</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -3940,7 +3940,7 @@
         <v>125843309</v>
       </c>
       <c r="B29" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -3940,7 +3940,7 @@
         <v>125843309</v>
       </c>
       <c r="B29" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -3940,7 +3940,7 @@
         <v>125843309</v>
       </c>
       <c r="B29" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -3940,7 +3940,7 @@
         <v>125843309</v>
       </c>
       <c r="B29" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -4059,7 +4059,7 @@
         <v>132135112</v>
       </c>
       <c r="B30" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -4059,7 +4059,7 @@
         <v>132135112</v>
       </c>
       <c r="B30" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -4059,7 +4059,7 @@
         <v>132135112</v>
       </c>
       <c r="B30" t="n">
-        <v>57132</v>
+        <v>57133</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96370805</v>
+        <v>104255473</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sumpskogen vid E12, Umeälvens delta och slätter, Vb</t>
+          <t>Obbolaön, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761601.5379005239</v>
+        <v>761572</v>
       </c>
       <c r="R2" t="n">
-        <v>7076870.580440815</v>
+        <v>7076818</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,98 +754,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96370862</v>
+        <v>104267447</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sumpskogen vid E12, Umeälvens delta och slätter, Vb</t>
+          <t>Sumpskogen vid E12, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761592.7228139872</v>
+        <v>761592</v>
       </c>
       <c r="R3" t="n">
-        <v>7076869.402088716</v>
+        <v>7076857</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,49 +851,43 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96370835</v>
+        <v>96370805</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,8 +912,16 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -996,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761590.3682953015</v>
+        <v>761602</v>
       </c>
       <c r="R4" t="n">
-        <v>7076892.34965267</v>
+        <v>7076871</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1029,19 +963,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,6 +977,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1069,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96370886</v>
+        <v>96370819</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1116,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761606.7046368989</v>
+        <v>761676</v>
       </c>
       <c r="R5" t="n">
-        <v>7076883.472116062</v>
+        <v>7076888</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1149,19 +1083,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,21 +1097,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1204,15 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96370938</v>
+        <v>96370835</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,35 +1124,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1256,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761561.9222628286</v>
+        <v>761590</v>
       </c>
       <c r="R6" t="n">
-        <v>7076853.933166469</v>
+        <v>7076892</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1289,27 +1184,18 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1328,15 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104255451</v>
+        <v>104255445</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>761549.0224591407</v>
+        <v>761637</v>
       </c>
       <c r="R7" t="n">
-        <v>7076751.828112532</v>
+        <v>7076779</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1401,19 +1282,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,37 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104255441</v>
+        <v>104255451</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1480,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761649.0178768341</v>
+        <v>761549</v>
       </c>
       <c r="R8" t="n">
-        <v>7076771.273017898</v>
+        <v>7076752</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1513,19 +1379,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,15 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104255445</v>
+        <v>104255459</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761636.7746196885</v>
+        <v>761566</v>
       </c>
       <c r="R9" t="n">
-        <v>7076779.156056687</v>
+        <v>7076834</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1625,19 +1476,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,15 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104267444</v>
+        <v>104267440</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1704,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761570.9183842726</v>
+        <v>761556</v>
       </c>
       <c r="R10" t="n">
-        <v>7076842.219464769</v>
+        <v>7076882</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1737,19 +1573,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,15 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104255459</v>
+        <v>104267443</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,17 +1648,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Obbolaön, Vb</t>
+          <t>Sumpskogen vid E12, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761566.2322147408</v>
+        <v>761576</v>
       </c>
       <c r="R11" t="n">
-        <v>7076834.263483238</v>
+        <v>7076857</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1864,21 +1685,11 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1887,31 +1698,41 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104267451</v>
+        <v>104267445</v>
       </c>
       <c r="B12" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,16 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1938,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761635.7961710589</v>
+        <v>761579</v>
       </c>
       <c r="R12" t="n">
-        <v>7076849.841767691</v>
+        <v>7076887</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1971,19 +1797,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,15 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104267443</v>
+        <v>104267448</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761575.9014702946</v>
+        <v>761592</v>
       </c>
       <c r="R13" t="n">
-        <v>7076857.321241158</v>
+        <v>7076850</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2098,19 +1909,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,15 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104255456</v>
+        <v>96370862</v>
       </c>
       <c r="B14" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,17 +1981,28 @@
           <t>(Schwein.) Murrill</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Obbolaön, Vb</t>
+          <t>Sumpskogen vid E12, Umeälvens delta och slätter, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761581.2027903795</v>
+        <v>761593</v>
       </c>
       <c r="R14" t="n">
-        <v>7076820.376206896</v>
+        <v>7076869</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2222,22 +2029,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2246,33 +2043,44 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104255474</v>
+        <v>104255441</v>
       </c>
       <c r="B15" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2304,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761514.0287268561</v>
+        <v>761649</v>
       </c>
       <c r="R15" t="n">
-        <v>7076781.408847106</v>
+        <v>7076771</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2337,19 +2145,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2376,37 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104255473</v>
+        <v>104255446</v>
       </c>
       <c r="B16" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2416,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761572.4610905374</v>
+        <v>761620</v>
       </c>
       <c r="R16" t="n">
-        <v>7076818.313875982</v>
+        <v>7076791</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2449,19 +2242,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2488,53 +2271,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104267445</v>
+        <v>104255448</v>
       </c>
       <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sumpskogen vid E12, Vb</t>
+          <t>Obbolaön, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761579.6712159989</v>
+        <v>761583</v>
       </c>
       <c r="R17" t="n">
-        <v>7076887.009204243</v>
+        <v>7076749</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2561,21 +2339,11 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2584,84 +2352,64 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104267440</v>
+        <v>104255449</v>
       </c>
       <c r="B18" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sumpskogen vid E12, Vb</t>
+          <t>Obbolaön, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761555.5860823627</v>
+        <v>761556</v>
       </c>
       <c r="R18" t="n">
-        <v>7076881.89043934</v>
+        <v>7076738</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2688,21 +2436,11 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2711,46 +2449,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104267442</v>
+        <v>104255456</v>
       </c>
       <c r="B19" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2778,17 +2496,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sumpskogen vid E12, Vb</t>
+          <t>Obbolaön, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761588.0491835175</v>
+        <v>761581</v>
       </c>
       <c r="R19" t="n">
-        <v>7076909.514195707</v>
+        <v>7076820</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2815,21 +2533,11 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2838,46 +2546,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104255446</v>
+        <v>104255466</v>
       </c>
       <c r="B20" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2909,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761619.7744368549</v>
+        <v>761539</v>
       </c>
       <c r="R20" t="n">
-        <v>7076790.64909515</v>
+        <v>7076792</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2942,19 +2630,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2984,12 +2662,7 @@
         <v>104255470</v>
       </c>
       <c r="B21" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3021,10 +2694,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761595.1278437491</v>
+        <v>761595</v>
       </c>
       <c r="R21" t="n">
-        <v>7076899.421530282</v>
+        <v>7076899</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3054,19 +2727,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3093,48 +2756,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104267441</v>
+        <v>104255471</v>
       </c>
       <c r="B22" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sumpskogen vid E12, Vb</t>
+          <t>Obbolaön, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>761578.1256438012</v>
+        <v>761623</v>
       </c>
       <c r="R22" t="n">
-        <v>7076900.23255433</v>
+        <v>7076878</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3161,21 +2824,11 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3184,46 +2837,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104267446</v>
+        <v>104255474</v>
       </c>
       <c r="B23" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3251,17 +2884,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen vid E12, Vb</t>
+          <t>Obbolaön, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>761595.5622126409</v>
+        <v>761514</v>
       </c>
       <c r="R23" t="n">
-        <v>7076867.412943782</v>
+        <v>7076781</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3288,21 +2921,11 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3311,86 +2934,61 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104267449</v>
+        <v>104267442</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sumpskogen vid E12, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>761599.9445367419</v>
+        <v>761588</v>
       </c>
       <c r="R24" t="n">
-        <v>7076841.518378659</v>
+        <v>7076909</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3420,21 +3018,11 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3443,6 +3031,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3459,15 +3062,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104255449</v>
+        <v>104267446</v>
       </c>
       <c r="B25" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3495,17 +3093,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Obbolaön, Vb</t>
+          <t>Sumpskogen vid E12, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>761556.432148384</v>
+        <v>761596</v>
       </c>
       <c r="R25" t="n">
-        <v>7076737.756592604</v>
+        <v>7076867</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3532,21 +3130,11 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3555,69 +3143,86 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104267448</v>
+        <v>96370886</v>
       </c>
       <c r="B26" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sumpskogen vid E12, Vb</t>
+          <t>Sumpskogen vid E12, Umeälvens delta och slätter, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>761592.0908626702</v>
+        <v>761607</v>
       </c>
       <c r="R26" t="n">
-        <v>7076850.211564665</v>
+        <v>7076883</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3641,22 +3246,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3665,70 +3260,66 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104267447</v>
+        <v>104267444</v>
       </c>
       <c r="B27" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3738,10 +3329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>761591.9451724973</v>
+        <v>761571</v>
       </c>
       <c r="R27" t="n">
-        <v>7076857.320558958</v>
+        <v>7076842</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3771,19 +3362,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3825,53 +3406,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104255471</v>
+        <v>104267452</v>
       </c>
       <c r="B28" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Obbolaön, Vb</t>
+          <t>Sumpskogen vid E12, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>761623.6688539741</v>
+        <v>761626</v>
       </c>
       <c r="R28" t="n">
-        <v>7076877.762327582</v>
+        <v>7076834</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3898,21 +3474,11 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3921,26 +3487,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125843309</v>
+        <v>96370938</v>
       </c>
       <c r="B29" t="n">
-        <v>58334</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,16 +3529,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3974,7 +3555,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3984,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>761593</v>
+        <v>761562</v>
       </c>
       <c r="R29" t="n">
-        <v>7076869</v>
+        <v>7076854</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4014,22 +3595,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4056,27 +3627,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132135112</v>
+        <v>96370956</v>
       </c>
       <c r="B30" t="n">
-        <v>57133</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4093,7 +3664,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4103,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>761643</v>
+        <v>761599</v>
       </c>
       <c r="R30" t="n">
-        <v>7076783</v>
+        <v>7076775</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4133,22 +3704,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4172,6 +3733,682 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>104267449</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sumpskogen vid E12, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>761600</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7076842</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132135112</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sumpskogen vid E12, Umeälvens delta och slätter, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>761643</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7076783</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125843309</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sumpskogen vid E12, Umeälvens delta och slätter, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>761593</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7076869</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>93928418</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fjolårsunge</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Björka, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>761545</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7076728</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-05-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-05-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tim Hofmeester</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tim Hofmeester</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>104267441</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sumpskogen vid E12, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>761578</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7076900</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>104267451</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sumpskogen vid E12, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>761636</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7076850</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41407-2022 artfynd.xlsx
+++ b/artfynd/A 41407-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255473</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96370805</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96370819</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96370835</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255445</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255451</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255459</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267440</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267443</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267445</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267448</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2074,6 +2139,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96370862</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2171,6 +2241,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255441</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2268,6 +2343,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255446</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2365,6 +2445,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255448</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2462,6 +2547,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255449</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2559,6 +2649,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255456</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2656,6 +2751,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255466</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2753,6 +2853,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255470</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2850,6 +2955,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255471</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2947,6 +3057,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104255474</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3059,6 +3174,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267442</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3171,6 +3291,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267446</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3291,6 +3416,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96370886</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3403,6 +3533,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267444</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3515,6 +3650,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267452</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3624,6 +3764,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96370938</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3733,6 +3878,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96370956</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3835,6 +3985,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267449</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3954,6 +4109,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132135112</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4073,6 +4233,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125843309</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4185,6 +4350,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93928418</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4297,6 +4467,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267441</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4409,8 +4584,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104267451</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>